--- a/docs/ad-name-cleanup.xlsx
+++ b/docs/ad-name-cleanup.xlsx
@@ -9,11 +9,15 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Dead Post IDs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="IFAD Ads Missing SIF ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Recoverable via Old SIF" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Needs Manual Fix" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="IFAD Ads Missing SIF ID" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dead Post IDs'!$A$1:$G$369</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'IFAD Ads Missing SIF ID'!$A$1:$H$1305</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Recoverable via Old SIF'!$A$1:$G$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Needs Manual Fix'!$A$1:$G$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'IFAD Ads Missing SIF ID'!$A$1:$H$1305</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -550,6 +554,43 @@
       <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Source: Meta Ads warehouse ae_table_view + Creator Hub posts/historic_posts, extracted 3 Jul 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Breakdown of the dead post IDs (added 3 Jul 2026):</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Recoverable via Old SIF</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>131</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Real legacy creators whose SIF was renumbered during dedup — the ads carry the retired ID. Creator Hub maps these to the canonical creator AUTOMATICALLY; no Meta edits needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Needs Manual Fix</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>13 ads name a real creator but a P-number they never had + 13 IDs that exist nowhere (typos, double-prefixes like SIFSIF/SSIF). These need correcting in Meta Ads Manager.</t>
         </is>
       </c>
     </row>
@@ -13505,6 +13546,5205 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G132"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Old Post ID (in ad name)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Old SIF</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Archive Username</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Canonical Creator (today)</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Ads</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Spend (INR)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Ad Names</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1819-P1</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1819</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>yaminimahant</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9441</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F2" s="8" t="n">
+        <v>885594.1899999999</v>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>CC+MU+TTB+OSP+IFAD-1PA-SIF-1819-P1-yaminimahant_15/12/25 | CC+MU+TTB+OSP+IFAD-SIF-1819-P1-yaminimahant_15/12/25 | CLP-SDVPL_VRP_RV_SIF-1819-P1-yaminimahant _IFAD_916_16112025_26/11/25_C0 - Copy | CLP-SDVPL_VRP_RV_SIF-1819-P1-yaminimahant _IFAD_916_16112025_26/11/25_C0 - Copy – Copy | HP-IFAD-SIF-1819-P1-yaminimahant_15/12/25_C0 – Copy | IFAD-SIF-1819-P1-yaminimahant_15/12/25 – Copy | IFAD-SIF-1819-P1-yaminimahant_15/12/25 – Copy 2 | IFAD-SIF-1819-P1-yaminimahant_15/12/25_C0 | SDFSK/SDVPL_VRP_RV_</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2219-P1</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2219</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>the_lakshmi_choudhary</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3976</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>878539.26</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>CTP-TW+IFAD+NA+OSP+SIF-2219-P1-khushiitiwariiii_19/01/26 – Copy | CTP-TW+IFAD+NA+OSP+SIF-2219-P1-khushiitiwariiii_19/01/26_C0 | CTP-TW+IFAD+NA+OSP+SIF-2219-P1-khushiitiwariiii_19/01/26_C0 - Copy | CTP-TW+IFAD+NA+OSP+SIF-2219-P1-khushiitiwariiii_19/01/26_C0 – Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2441-P1</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2441</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>ritika_hans</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9458</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>716896.7</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>CTP+IFAD+NA+OSP+SIF-2441-P1-ritika_hans_15/01/26 - Copy | CTP+IFAD+NA+OSP+SIF-2441-P1-ritika_hans_15/01/26 – Copy | CTP+IFAD+NA+OSP+SIF-2441-P1-ritika_hans_15/01/26_C0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2604-P2</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2604</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>aatisha.sharma</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9460</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>570373.02</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDFLK+IFAD+NA+IHP+SIF-2604-P2-aatisha.sharma_02/02/26 – Copy | CLP-SDFLK+IFAD+NA+IHP+SIF-2604-P2-aatisha.sharma_02/02/26_C0 | CLP-SDFLK+IFAD+NA+IHP+SIF-2604-P2-aatisha.sharma_02/02/26_C0 - Copy | CLP-SDFSK+IFAD+OF-NA+OSP+SIF-2604-P2-aatisha.sharma_03/02/26- ad off</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1705-P1</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1705</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>drushti.ramrakhyani</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9436</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>267225.94</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDAWP+IFAD+NA+OSP+SIF-1705-P1-drushti.ramrakhyani-22/04/26 - Copy | CLP-SDAWP+IFAD+NA+OSP+SIF-1705-P1-drushti.ramrakhyani-22/04/26_C0 | CLP-SDAWP+IFAD+NA+OSP+SIF-1705-P1-drushti.ramrakhyani-22/04/26_C0 - Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4030-P1</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4030</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>aakashdhas_</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9491</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>204057.35</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SMFLK+IFAD+NA+OSP+1PA-SIF-4030-P1-aakashdhas_-19/02/26 | CLP-SMFLK+IFAD+NA+OSP+SIF-4030-P1-aakashdhas_-19/02/26 – Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2700-P1</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2700</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>sakshi.agarwallll</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9464</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>192446.12</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>IFAD-1PA-SIF-2700-P1-sakshi.agarwallll_20/12/25 | IFAD-SIF-2700-P1-sakshi.agarwallll_20/12/25 | IFAD-SIF-2700-P1-sakshi.agarwallll_20/12/25 – Copy | IFAD-SIF-2700-P1-sakshi.agarwallll_20/12/25 – Copy 2 | IFAD-SIF-2700-P1-sakshi.agarwallll_20/12/25 – Copy 3 | SIF-2700-P1-sakshi.agarwallll_20/12/25 – Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>SIF-151-P3</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>SIF-151</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>twinning_damsel</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9432</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>107543.48</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>CTP-BST_IFAD–SIF-151-P3-twinning_damsel_16/12/25 – Copy_C0 | CTP-BST_IFAD–SIF-151-P3-twinning_damsel_16/12/25 – Copy_C0 - Copy | CTP-BST_IFAD–SIF-151-P3-twinning_damsel_16/12/25_C0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1466-P1</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1466</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>sanviikadam</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9430</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>106909.41</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>1PA-SIF-1466-P1-sanviikadam_IFAD_15/11/25 | 1PA-SIF-1466-P1-sanviikadam_IFAD_15/11/25 - Copy | CLP-SDFLK_IFAD-SIF-1466-P1-sanviikadam_16/12/25 | CLP-SDFLK_IFAD-SIF-1466-P1-sanviikadam_16/12/25 – Copy | SIF-1466-P1-sanviikadam_IFAD_15/11/25 – Copy | SIF-1466-P1-sanviikadam_IFAD_15/11/25 – Copy 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2055-P1</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2055</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>raginiigupta6</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9424</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>101675.31</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>CLP+IFAD+OF-RH+OSP+BR_SIF-2055-p1-ishhxaaa_05/12/25 | CLP-SDALS+IFAD+OF-RH+OSP+SDALS_SIF-2055-p1-ishhxaaa_05/12/25 | CLP-SDALS+IFAD+OF-RH+OSP+SDALS_SIF-2055-p1-ishhxaaa_05/12/25 - Copy_C0 | CLP-SDALS+IFAD+OF-RH+OSP+SDALS_SIF-2055-p1-ishhxaaa_05/12/25 - Copy_C0 – Copy | CLP-SDALS+MU+NA+IHP+IFAD_SIF-2055-P1-raginiigupta6_SDALS_31/12/25 | CLP-SDFLK+IFAD+NA+OSP+SIF-2055-P1-raginiigupta6_13/01/26 – Copy | CLP-SDFLK+IFAD+NA+OSP+SIF-2055-P1-raginiigupta6_13/01/26 – Copy 2 | CLP-SDFLK+IFAD+NA+OSP+SIF-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1705-P2</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1705</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>drushti.ramrakhyani</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9436</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>101045.07</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>CC+MU+SDWLP- ERROR+OSP+IFAD_SIF-1705-P2-drushti.ramrakhyani_SDWLP_26/12/25-2 - Copy | CC+MU+TTB+OSP+IFAD_SIF-1705-P2-drushti.ramrakhyani_SDWLP_26/12/25-2 - Copy | HP-IFAD_SIF-1705-P2-drushti.ramrakhyani_SDWLP_26/12/25-2 - Copy | IFAD_SIF-1705-P2-drushti.ramrakhyani_SDWLP_26/12/25 | IFAD_SIF-1705-P2-drushti.ramrakhyani_SDWLP_26/12/25 – Copy | IFAD_SIF-1705-P2-drushti.ramrakhyani_SDWLP_26/12/25-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1705-P3</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1705</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>drushti.ramrakhyani</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9436</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>93973.17999999999</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDRPT+IFAD+NA+OSP+SIF-1705-P3-drushti.ramrakhyani-18/04/26 -A0 | CLP-SDWLP+IFAD+NA+OSP+SIF-1705-P3-drushti.ramrakhyani-18/04/26 - Copy | CLP-SDWLP+IFAD+NA+OSP+SIF-1705-P3-drushti.ramrakhyani-18/04/26_C0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4872-P1</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4872</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>yashikasinghall</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9431</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>77359.56</v>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>CTP-COO+IFAD-MU+NA+OSP+1PA-SIF-4872-P1-yashikasinghall-02/04/26 | CTP-STL+IFAD-MU+NA+OSP+SIF-4872-P1-yashikasinghall-02/04/26 – Copy | CTP-STL+IFAD-MU+NA+OSP+SIF-4872-P1-yashikasinghall-02/04/26_C0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3877-P1</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3877</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>lifewith_ayushii</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9489</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>69129.71000000001</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDFSK+IFAD+OF-NA+OSP+SIF-3877-P1-lifewith_ayushii-13/02/26 – Copy | CLP-SDFSK+IFAD+OF-NA+OSP+SIF-3877-P1-lifewith_ayushii-13/02/26_C0 | CLP-SDFSK+IFAD+OF-NA+OSP+SIF-3877-P1-lifewith_ayushii-13/02/26_C0 – Copy | CTP-WTW+IFAD+NA+OSP+SIF-3877-P1-lifewith_ayushii_07/01/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5002-P1</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5002</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>pinkyschoudhary</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9510</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>66129.35000000001</v>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDAFD+IFAD-MU+NA+OSP+SIF-5002-P1-pinkyschoudhary-02/04/26_C0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2210-P1</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2210</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>shakuo</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>— (handle changed / not live)</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>64332.13</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>CTP-MTW+IFAD+NA+OSP+1PA-SIF-2210-P1-shubhammsharmaa__09/01/26_H0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2997-P1</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2997</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>khushimaheswary</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9469</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>63124.51</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>HP-IFAD_SIF-2997-P1-khushimaheswary_SUZNS_31/12/25 - Copy 2 | IFAD_SIF-2997-P1-khushimaheswary_SUPFH_30/12/25 | IFAD_SIF-2997-P1-khushimaheswary_SUZNS_31/12/25 - Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4042-P1</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4042</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>prayagkoshiyaofficial</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9492</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>61693.67</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>CTP-SMFSK+IFAD+NA+OSP+1PA-SIF-4042-P1-prayagkoshiyaofficial-28/03/26_H0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3757-P1</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3757</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>amrutha_naiduu__</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9488</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>52183.66</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>CTP-COO+IFAD+NA+OSP+1PA-SIF-3757-P1-amrutha_naiduu__-16/02/26_C0 | CTP-COO+IFAD+NA+OSP+SIF-3757-P1-amrutha_naiduu__-16/02/26_C0 | CTP-COO+IFAD+NA+OSP+SIF-3757-P1-amrutha_naiduu__-16/02/26_C0 – Copy | CTP-COO+IFAD+NA+OSP+SIF-3757-P1-amrutha_naiduu__-16/02/26_C0 – Copy 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>SIF-947-P1</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>SIF-947</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>dishaa_bharti</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9561</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>40975.84</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>CTP-WW+IFAD+NA+OSP+SIF-947-P1-dishaa_bharti_17/01/26_C0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>SIF-291-P4</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>SIF-291</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>adt_singhal_</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9465</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>33858.52</v>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>CTP+IFAD+NA+OSP+SIF-291-P4-adt_singhal__15/01/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1285-P1</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1285</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>shiningsstory</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9425</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>30612.36</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>CLP-BSW_IFAD-SIF-1285-P1-shiningsstory_22/11/25 | CLP-BSW_IFAD-SIF-1285-P1-shiningsstory_22/11/25 – Copy | PDP-SDFSK+IFAD+NA+IHP+SDFSK_VRP_MS_SIF-1285-P1-shiningsstory_IFAD_916_080925_12/09/25 | PDP-SDFSK+IFAD+NA+IHP+SDFSK_VRP_MS_SIF-1285-P1-shiningsstory_IFAD_916_080925_12/09/25 - Copy | PDP-SDFSK+IFAD+NA+IHP+SDFSK_VRP_MS_SIF-1285-P1-shiningsstory_IFAD_916_080925_12/09/25 – Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>SIF-186-P1</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>SIF-186</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>devna_sahrawat</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9414</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>28713.3</v>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>CTP-BST_IFAD–SIF-186-P1-devna_sahrawat_16/12/25 | CTP-BST_IFAD–SIF-186-P1-devna_sahrawat_16/12/25 – Copy | CTP-BST_IFAD–SIF-186-P1-devna_sahrawat_16/12/25 – Copy - Copy-AD-OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2123-P1</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2123</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>yogitamalviyaa</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9449</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>26718.77</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDFSK+IFAD-MU+OF-RH+OSP+IFAD_SIF-2123-P1-yogitamalviyaa_13/12/25 | CTP-COO_IFAD-SIF-2123-P1-yogitamalviyaa_16/12/25 – Copy | CTP-COO_IFAD-SIF-2123-P1-yogitamalviyaa_16/12/25 – Copy 2 | CTP-COO_IFAD-SIF-2123-P1-yogitamalviyaa_16/12/25_C0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1421-P1</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1421</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>yours.laksh17</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9428</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>26252.84</v>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SMFLK+IFAD+NA+IHP+-SIF-1421-P1-yours.laksh17_16/12/25_H0 | CLP-SMFLK+IFAD+NA+IHP+-SIF-1421-P1-yours.laksh17_16/12/25_H0 – Copy | CTP-MSA+IFAD-MU+NA+OSP+1PA-SIF-1421-P1-yours.laksh17-19/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>SIF-939-P2</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>SIF-939</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>aestheticsbyshruti</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9560</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>26100.59</v>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDFSK+IFAD+OF-RH+OSP+SIF-939-P2-aestheticsbyshruti_06/12/25 | CLP-SDFSK+IFAD+OF-RH+OSP+SIF-939-P2-aestheticsbyshruti_06/12/25_C0 | CLP-SDFSK+IFAD+OF-RH+OSP+SIF-939-P2-aestheticsbyshruti_06/12/25_C0 - Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1788-P1</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1788</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>tanyaa.yaaa</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9437</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>25747.7</v>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>BR_VRP_RV_SIF-1788-P1-tanyaa.yaaa_IFAD_916_12112025_26/11/25_C0 | BR_VRP_RV_SIF-1788-P1-tanyaa.yaaa_IFAD_916_12112025_26/11/25_C0 – Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3006-P1</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3006</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>muskan_mintri</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9470</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>23670.67</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>CLP+IFAD-MU+OF-RH+OSP+COO_SIF-3006-P1-muskan_mintri_13/12/25 | CTP-COO_IFAD-SIF-3006-P1-muskan_mintri_16/12/25 – Copy | CTP-COO_IFAD-SIF-3006-P1-muskan_mintri_16/12/25 – Copy 2 | CTP-COO_IFAD-SIF-3006-P1-muskan_mintri_16/12/25 – Copy 3 | CTP-COO_IFAD-SIF-3006-P1-muskan_mintri_16/12/25 – Copy 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2950-P1</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2950</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>outfitwithsky</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9468</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>22316.91</v>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SMFLK+IFAD+NA+OSP+SIF-2950-P1-outfitwithsky_09/01/26 | CLP-SMFLK+IFAD+NA+OSP+SIF-2950-P1-outfitwithsky_09/01/26 – Copy | CLP-SMFLK+IFAD+NA+OSP+SIF-2950-P1-outfitwithsky_09/01/26 – Copy 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5894-P1</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5894</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>amann4real</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9527</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>22150.98</v>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SMCFS+IFAD+NA+OSP+SIF-5894-P1-amann4real-09/04/26_H0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1810-P1</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1810</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>_s.h.i.r.i.n.__</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>— (handle changed / not live)</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>19554.34</v>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDFLK+MU+NA+OSP+SIF-1810-P1-_s.h.i.r.i.n.___06/01/26 | CLP-SDFLK+MU+NA+OSP+SIF-1810-P1-_s.h.i.r.i.n.___06/01/26 – Copy | CLP-SDFSK+IFAD+NA+OSP+SIF-1810-P1-_s.h.i.r.i.n.___06/01/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1788-P3</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1788</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>tanyaa.yaaa</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9437</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>18536.24</v>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDCSS+IFAD+NA+OSP+SIF-1788-P3-tanyaa.yaaa-28/03/26 | CLP-SDCSS+IFAD+NA+OSP+SIF-1788-P3-tanyaa.yaaa-28/03/26 – Copy | CLP-SDCSS+IFAD+NA+OSP+SIF-1788-P3-tanyaa.yaaa-28/03/26 – Copy 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1038-P1</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1038</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>kajal._.chawla</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9411</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>15258.81</v>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>CTP-SLP+IFAD+NA+IHP+SDFSKEC/SDCPPB_VRP_ST_SIF-1038-P1-kajal._.chawla_IFAD_916_240725_19/09/25 | CTP-SLP+IFAD+NA+IHP+SDFSKEC/SDCPPB_VRP_ST_SIF-1038-P1-kajal._.chawla_IFAD_916_240725_19/09/25 - Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2194-P2</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2194</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>aprayadav</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9452</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>13190.28</v>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDFSK_IFAD–SIF-2194-P2-aprayadav_16/12/25 – Copy | CLP-SDFSK_IFAD–SIF-2194-P2-aprayadav_16/12/25 – Copy - Copy | CLP-SDFSK_IFAD–SIF-2194-P2-aprayadav_16/12/25_C0 | CLP-SDFSK_IFAD–SIF-2194-P2-aprayadav_16/12/25_C0 - Copy-AD-OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3581-P1</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3581</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>suramya.bharadwaj</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9484</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>9897.959999999999</v>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDAFD+IFAD+NA+OSP+SIF-3581-P1-suramya.bharadwaj-16/02/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3287-P1</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3287</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>heykhhushi</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9477</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>9838.01</v>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>CTP-BST+IFAD-MU+NA+OSP+SIF-3287-P1-heykhhushi-18/02/26 | CTP-BST+IFAD-MU+NA+OSP+SIF-3287-P1-heykhhushi-18/02/26 – Copy | CTP-BST+IFAD-MU+NA+OSP+SIF-3287-P1-heykhhushi-18/02/26 – Copy 2 | CTP-BST+IFAD-MU+NA+OSP+SIF-3287-P1-heykhhushi-18/02/26 – Copy AD OFF | CTP-BST+IFAD-MU+NA+OSP+SIF-3287-P1-heykhhushi-18/02/26-AD-OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7812-P1</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7812</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>shivamsachdeva98</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3040</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>7983.45</v>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SMFRT+IFAD+NA+IHP+1PA-SIF-7812-P1-shivamsachdeva98 -27/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>SIF-839-P3</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>SIF-839</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>shefalithapa2</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9421</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>7774.53</v>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDFLK+IFAD+NA+OSP+SIF-839-P3-shefalithapa2_15/01/26 – Copy | CLP-SDFLK+IFAD+NA+OSP+SIF-839-P3-shefalithapa2_15/01/26_C0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1855-P1</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1855</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>dikshitapunetha</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9443</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>6784.67</v>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>CLP+IFAD+OF-RH+OSP+BST_SIF-1855-p1-delulu_here_05/12/25 | CLP-SDFLK+MU+OF-RH+IHP+SDFLK_SIF-1855-p1-delulu_here_05/12/25 | CTP-BST+IFAD+NA+OSP+SIF-1855-P1-dikshitapunetha-21/04/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1909-P1</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1909</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>saniha.s.jois_</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>— (handle changed / not live)</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>6550.38</v>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDFLK+IFAD+OF-RH+IHP+SDFLKNB_VRP_RV_SIF-1909-P1-saniha.s.jois__IFAD_916_23112025_29/11/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5241-P1</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5241</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>_aadityanagpal_</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9515</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>5805.09</v>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>CTP-SMLS+IFAD+NA+OSP+1PA-SIF-5241-P1-_aadityanagpal_-26/02/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2944-P1</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2944</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>ram_sharma88</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9467</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>4260.23</v>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>CLP-MTW+IFAD+NA+OSP+SIF-2944-P1-ram_sharma88_13/01/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>SIF-445-P2</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>SIF-445</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>srishhti._</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9501</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>3940.58</v>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDFLK+IFAD+NA+OSP+SIF-445-P2-srishhti._22/04/26 | CLP-SDFLK+IFAD+NA+OSP+SIF-445-P2-srishhti._22/04/26 - Copy | CLP-SDFLK+IFAD+NA+OSP+SIF-445-P2-srishhti._3/05/26 - Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1817-P1</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1817</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>khushimodii</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9440</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>3910.5</v>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>CTP-TW+IFAD+NA+OSP+SIF-1817-P1-khushimodii_22/01/26 | CTP-TW+IFAD+NA+OSP+SIF-1817-P1-khushimodii_22/01/26 – Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2185-P2</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2185</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>themansikhatri</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9451</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>3453.39</v>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>CTP-WW+IFAD-MU+NA+OSP+SIF-2185-P2-themansikhatri_916_ITE-Jan-414_16/01/26 | CTP-WW+IFAD-MU+NA+OSP+SIF-2185-P2-themansikhatri_916_ITE-Jan-414_16/01/26 – Copy | CTP-WW+IFAD-MU+NA+OSP+SIF-2185-P2-themansikhatri_916_ITE-Jan-414_16/01/26 – Copy 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4999-P1</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4999</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>__snnehaa_</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9509</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>3261.5</v>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDFSK+IFAD+NA+OSP+1PA-SIF-4999-P1-__snnehaa_-6/06/26 | CLP-SDFSK+IFAD+NA+OSP+SIF-4999-P1-__snnehaa_-6/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4783-P1</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4783</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>palaknagia</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9505</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>3178.97</v>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>CTP-TW+IFAD-MU+NA+OSP+SIF-4783-P1-palaknagia-02/04/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2531-P1</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2531</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>palaksharmax7</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9459</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>2894.74</v>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDFLK+IFAD+NA+OSP+SIF-2531-P1-palaksharmax7_13/01/26 | IFAD_SIF-2531-P1-palaksharmax7_SDFLK_30/12/25 | IFAD_SIF-2531-P1-palaksharmax7_SDWLP_30/12/25 | IFAD_SIF-2531-P1-palaksharmax7_SDWLP_30/12/25 - Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4331-P1</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4331</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>iramalhotra3</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9500</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" s="8" t="n">
+        <v>2633.4</v>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDFLK+IFAD+NA+OSP+SIF-4331-P1-iramalhotra3-02/04/26 | CLP-SDFLK+IFAD+NA+OSP+SIF-4331-P1-iramalhotra3-02/04/26 - Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2687-P3</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2687</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>aboutmansii</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9463</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>2401.74</v>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>CTP-TW+IFAD-MU+NA+OSP+SIF-2687-P3-aboutmansii-13/02/26 | CTP-TW+IFAD-MU+NA+OSP+SIF-2687-P3-aboutmansii-13/02/26 – Copy | CTP-TW+IFAD-MU+NA+OSP+SIF-2687-P3-aboutmansii-13/02/26 – Copy-AD-OFF | CTP-WTW+IFAD-MU+NA+OSP+SIF-2687-P3-aboutmansii_07/01/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3948-P1</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3948</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>wasim._.officiall</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>— (handle changed / not live)</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="8" t="n">
+        <v>2228.07</v>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SMFLK+IFAD+NA+OSP+1PA-SIF-3948-P1-wasim._.officiall-09/03/26_H0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3755-P1</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3755</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>esh.bliss</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9487</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>2124.19</v>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDFLK+IFAD+NA+OSP+1PA-SIF-3755-P1-esh.bliss-15/04/26 | CLP-SDFLK+IFAD+NA+OSP+1PA-SIF-3755-P1-esh.bliss-15/04/26 - Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7263-P1</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7263</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>arya.powar</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9543</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" s="8" t="n">
+        <v>1652.34</v>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>CTP-SDFAK+IFAD-MU+NA+OSP+1PA-SIF-7263-P1-arya.powar-5/06/26 | CTP-SDFAK+IFAD-MU+NA+OSP+1PA-SIF-7263-P1-arya.powar-9/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>SIF-6442-P1</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>SIF-6442</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>shh.reya.aaa</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9534</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>1423.99</v>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDCPT+IFAD-MU+NA+OSP+1PA-SIF-6442-P1-shh.reya.aaa-22/05/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1259-P1</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1259</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>nidhhiiiiii</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9422</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F56" s="8" t="n">
+        <v>1319.4</v>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>IFAD-SIF-1259-P1-nidhhiiiiii_15/12/25 | IFAD-SIF-1259-P1-nidhhiiiiii_15/12/25 – Copy | IFAD-SIF-1259-P1-nidhhiiiiii_15/12/25 – Copy 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>SIF-6023-P1</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>SIF-6023</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>riaapanwar</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9529</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>1153.24</v>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDCPT+IFAD+NA+OSP+SIF-6023-P1-riaapanwar-28/03/26 – Copy 2-ADD-OFF | CLP-SDCPT+IFAD+NA+OSP+SIF-6023-P1-riaapanwar-28/03/26-AD-OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>SIF-554-P2</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>SIF-554</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>prraacchhee</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9521</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="8" t="n">
+        <v>1111.42</v>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>CTP-SDFLS+IFAD-MU+NA+OSP+SIF-554-P2-prraacchhee-30/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4067-P1</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4067</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>pinterest__muffin</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9494</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F59" s="8" t="n">
+        <v>1023.15</v>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDALS+IFAD-MU+NA+IHP+SIF-4067-P1-pinterest__muffin_28/01/26 – Copy | CLP-SDALS+MU+NA+IHP+SIF-4067-P1-pinterest__muffin_28/01/26 – Copy 2 | CLP-SDALS+MU+NA+IHP+SIF-4067-P1-pinterest__muffin_28/01/26 – Copy-ad off | CLP-SDALS+MU+NA+IHP+SIF-4067-P1-pinterest__muffin_28/01/26- ad off | SDAWPBL/SDALS_VRP_ST_SIF-4067-P1-pinterest__muffin_IFAD_260625</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1796-P2</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1796</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>shubhisrivastava__</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9438</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="8" t="n">
+        <v>971.47</v>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDALS+IFAD+NA+OSP+SIF-1796-P2-shubhisrivastava__10/05/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3411-P2</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3411</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>aridhi_gupta</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9480</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>935.91</v>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDCSS+IFAD-MU+NA+OSP+SIF-3411-P2-aridhi_gupta-14/05/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>SIF-6420-P1</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>SIF-6420</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>vidishajain._</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>— (handle changed / not live)</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="8" t="n">
+        <v>923.33</v>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>CLP-CTP+IFAD+NA+OSP+1PA-SIF-6420-P1-vidishajain.-14/05/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1471-P1</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1471</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>moksha_punmiya</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9481</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="8" t="n">
+        <v>790.78</v>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>SDFLKHP/SDAWPBE_VRP_MS_SIF-1471-P1-yashikasinghall_IFAD_916_06112025_26/11/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4651-P1</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4651</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>24_manvi</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9503</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F64" s="8" t="n">
+        <v>768.03</v>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>CTP-COO+IFAD+NA+OSP+SIF-4651-P1-24_manvi-05/03/36 | CTP-COO+IFAD+NA+OSP+SIF-4651-P1-24_manvi-05/03/36 – Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7572-P1</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7572</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>paras_soul</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9526</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="8" t="n">
+        <v>706.55</v>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>CTP-SMDPT+IFAD+NA+IHP+SIF-7572-P1-paras_soul-30/05/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4078-P1</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4078</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>kashish.sipaiya</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9412</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="8" t="n">
+        <v>673.8</v>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDALS+IFAD+NA+OSP+SIF-4078-P1-kashish.sipaiya_02/02/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4989-P1</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4989</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>apekshaaa_14</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9508</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="8" t="n">
+        <v>586.12</v>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDFSK+IFAD+NA+OSP+1PA-SIF-4989-P1-apekshaaa_14-6/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3982-P2</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3982</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>khushimodiii</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>— (handle changed / not live)</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="8" t="n">
+        <v>551.16</v>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDELKB+IFAD-MU+NA+OSP+SIF-3982-P2-khushimodiii-02/04/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1870-P1</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1870</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>jenzfits</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9419</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F69" s="8" t="n">
+        <v>528.74</v>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDFSK+IFAD+OF-RH+OSP+SIF-1870-P1-jenzfits_06/12/25 | CLP-SDFSK+IFAD+OF-RH+OSP+SIF-1870-P1-jenzfits_06/12/25 - Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2194-P3</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2194</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>aprayadav</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9452</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="8" t="n">
+        <v>519.12</v>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDASP+IFAD+NA+OSP+SIF-2194-P3-aprayadav-14/03/26-AD-OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>SIF-6030-P2</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>SIF-6030</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>aridhi_gupta</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9480</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="8" t="n">
+        <v>505.31</v>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDCPT+IFAD-MU+NA+OSP+SIF-6030-P2-aridhi_gupta-27/05/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7175-P1</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7175</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>yama_soni</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9542</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="8" t="n">
+        <v>455.42</v>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>CTP-KW+IFAD-MU+NA+IHP+1PA-SIF-7175-P1-yama_soni-9/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4889-P1</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4889</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>sonamsharmaa</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9507</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F73" s="8" t="n">
+        <v>454.75</v>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>CTP-TW+IFAD+NA+OSP+SIF-4889-P1-sonamsharmaa-26/02/26 | CTP-TW+IFAD+NA+OSP+SIF-4889-P1-sonamsharmaa-26/02/26 – Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1566-P1</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1566</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>devanshyyii</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9413</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F74" s="8" t="n">
+        <v>424.77</v>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>CLP+IFAD+OF-RH+OSP+BR_IFAD_SIF-1566-P1-devanshyyii_05/12/25 | CLP-SDFSK+IFAD+OF-RH+IHP+SDFSK_IFAD_SIF-1566-P1-devanshyyi_05/12/25 | CLP-SDFSK+IFAD+OF-RH+IHP+SDFSK_IFAD_SIF-1566-P1-devanshyyi_05/12/25 - Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7588-P1</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7588</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>riyapathar.e</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9550</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="8" t="n">
+        <v>397.63</v>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>CTP-SDFAK+IFAD-MU+NA+OSP+SIF-7588-P1- riyapathar.e -27/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1664-P1</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1664</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>anishagambhiir</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9435</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F76" s="8" t="n">
+        <v>381.03</v>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDRPT+IFAD+NA+IHP+SIF-1664-P1-anishagambhiir-2/05/26 | CLP-SDRPT+IFAD+NA+IHP+SIF-1664-P1-anishagambhiir-2/05/26 - Copy | CLP-SDRPT+IFAD+NA+OSP+1PA-SIF-1664-P1-anishagambhiir-26/05/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3997-P1</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3997</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>mishikaaverma</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9490</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>362.67</v>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>CTP-COO+IFAD+NA+OSP+SIF-3997-P1-mishikaaverma-26/03/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2017-P1</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2017</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>_divyakataria</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9445</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="8" t="n">
+        <v>320.41</v>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDFLK+IFAD-MU+NA+OSP+SIF-2017-P1-_divyakataria_916_ITE-Jan-421_16/01/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>SIF-73-P4</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>SIF-73</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>shivangimishra_</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9545</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="8" t="n">
+        <v>313.83</v>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDAFD+IFAD+NA+OSP+SIF-73-P4-shivangimishra_-02/04/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5274-P1</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5274</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>tanu.thakurrr</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9516</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="8" t="n">
+        <v>280.29</v>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDASP+IFAD+NA+OSP+SIF-5274-P1-tanu.thakurrr-18/03/26-AD-OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3124-P1</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3124</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>purva_bhumak</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9472</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="8" t="n">
+        <v>272.68</v>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDAWP+MU+NA+IHP+SIF-3124-P1-purva_bhumak-05/03/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>SIF-6740-P1</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>SIF-6740</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>abhinavakarsh</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9536</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="8" t="n">
+        <v>265.66</v>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SMDPT+IFAD+NA+IHP+1PA-SIF-6740-P1-abhinavakarsh-10/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4390-P1</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4390</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>prayagkoshiyaofficial</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9492</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="8" t="n">
+        <v>264.01</v>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SMCP+IFAD+NA+OSP+1PA-SIF-4390-P1-prayagkoshiyaofficial-03/04/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>SIF-151-P4</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>SIF-151</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>twinning_damsel</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9432</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="8" t="n">
+        <v>251.09</v>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>CLP-BST+IFAD-MU+NA+OSP+SIF-151-P4-twinning_damsel-13/02/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3346-P1</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3346</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>the.kashishshah</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9478</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F85" s="8" t="n">
+        <v>215.8</v>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>CTP-TW+IFAD+NA+OSP+SIF-3346-P1-the.kashishshah_22/01/26 – Copy | CTP-TW+IFAD+NA+OSP+SIF-3346-P1-the.kashishshah_22/01/26-AD-OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4269-P1</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4269</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>simraninprogress</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9498</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="8" t="n">
+        <v>201.42</v>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>CTP-BST+IFAD-MU+NA+OSP+SIF-4269-P1-simraninprogress-20/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>SIF-6373-P1</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>SIF-6373</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>chhaviisingh_</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9532</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="8" t="n">
+        <v>196.19</v>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>CTP-BCO+IFAD+NA+OSP+1PA-SIF-6373-P1-chhaviisingh_-2/05/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5445-P1</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5445</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>_lumosnox</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9520</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F88" s="8" t="n">
+        <v>194.93</v>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SMCSS+IFAD+NA+IHP+SIF-5445-P1-_lumosnox-3/05/26 | CLP-SMCSS+IFAD+NA+IHP+SIF-5445-P1-_lumosnox-3/05/26 - Copy | CTP-SMCSS+IFAD+NA+OSP+SIF-5445-P1-_lumosnox-3/05/26 - Copy 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4065-P1</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4065</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>beyond_aditiiii</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9493</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F89" s="8" t="n">
+        <v>177.25</v>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDFLK+IFAD-MU+NA+OSP+1PA-SIF-4065-P1-beyond_aditiiii-9/05/26 | CLP-SDFLK+IFAD-MU+NA+OSP+1PA-SIF-4065-P1-beyond_aditiiii-9/05/26 - Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5858-P2</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5858</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>iammahendrapandey</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9525</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="8" t="n">
+        <v>175.79</v>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>CTP-SMDPT+IFAD+NA+IHP+SIF-5858-P2-iammahendrapandey-28/05/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2031-P1</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2031</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>p.pushpendra</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9446</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="8" t="n">
+        <v>170.5</v>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>CTP-MTW+IFAD+NA+OSP+SIF-2031-P1-p.pushpendra_09/01/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5593-P1</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5593</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>blushwithsakshi</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9522</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F92" s="8" t="n">
+        <v>170.09</v>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>CTP-BST+IFAD-MU+NA+OSP+SIF-5593-P1-blushwithsakshi-02/04/26 | CTP-BST+IFAD-MU+NA+OSP+SIF-5593-P1-blushwithsakshi-02/04/26 – Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>SIF-61-P3</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>SIF-61</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>muskan_mintri</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9470</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="8" t="n">
+        <v>140.76</v>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>SDFSKMA_VRP_muskan_mintri-SIF-61-p3_916_010725</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1464-P1</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1464</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>arijit_biswas_arju</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9429</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" s="8" t="n">
+        <v>123.43</v>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>CLP-MSA+IFAD+NA+OSP+1PA-SIF-1464-P1-arijit_biswas_arju-21/04/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3424-P1</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3424</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>moksha_punmiya</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9481</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" s="8" t="n">
+        <v>119.07</v>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDFSK+IFAD+NA+OSP+SIF-3424-P1-moksha_punmiya-06/03/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3605-P1</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3605</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>_farishte_</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>— (handle changed / not live)</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="8" t="n">
+        <v>86.15000000000001</v>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDFSK+IFAD+NA+OSP+SIF-3605-P1-_farishte_-26/03/26-AD-OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2043-P1</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2043</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>nidhhiiiiii</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9422</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="8" t="n">
+        <v>79.91</v>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDALS+IFAD-MU+NA+OSP+1PA-SIF-2043-P1-nidhhiiiiii-24/04/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2123-P2</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2123</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>yogitamalviyaa</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9449</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="8" t="n">
+        <v>79.33</v>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>CTP-COO+IFAD-MU+NA+OSP+SIF-2123-P2-yogitamalviyaa-26/03/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>SIF-21-P1</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>SIF-21</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>arjit_biswas_arju</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>— (handle changed / not live)</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="8" t="n">
+        <v>72.11</v>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SMFSK+IFAD+NA+OSP+SIF-21-P1-arjit_biswas_arju_09/01/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4887-P1</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4887</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>gaurislookbook</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9506</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="8" t="n">
+        <v>70.45</v>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>CTP-BST+IFAD+NA+OSP+SIF-4887-P1-gaurislookbook-31/03/26-AD-OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3010-P1</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3010</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>utkarsh_shhh</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9471</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F101" s="8" t="n">
+        <v>62.86</v>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>CLP-MSA+IFAD+NA+OSP+1PA-SIF-3010-P1-utkarsh_shhh-17/04/26 | CLP-MSA+IFAD-MU+NA+OSP+1PA-SIF-3010-P1-SIF-2921-P1-_ayan_ansariiiii-17/04/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3247-P3</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3247</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>tanya.saini__</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9474</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="8" t="n">
+        <v>60.23</v>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDELPT+IFAD+NA+OSP+SIF-3247-P3-tanya.saini__-28/03/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7534-P1</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7534</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>isha_agarwal.09</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>— (handle changed / not live)</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" s="8" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>CTP-SDFAK+IFAD-MU+NA+OSP+1PA-SIF-7534-P1- isha_agarwal.09-5/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7826-P1</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7826</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>outfitwithsky</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9468</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="8" t="n">
+        <v>56.61</v>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>CTP-SMDPT+IFAD-MU+NA+IHP+1PA-SIF-7826-P1-outfitwithsky -20/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7274-P1</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7274</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>naman_matta</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9544</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F105" s="8" t="n">
+        <v>41.82</v>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>CTP-SMFRT+IFAD-MU+NA+IHP+SIF-7274-P1-naman_matta-23/05/26 | CTP-SMFRT+IFAD-MU+NA+IHP+SIF-7274-P1-naman_matta-23/05/26 - Copy | CTP-SMFRT+IFAD-MU+NA+IHP+SIF-7274-P1-naman_matta-23/05/26 - Copy 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5159-P1</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5159</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>piyushhhhpundir_</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9514</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="8" t="n">
+        <v>26.97</v>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>CLP-MSA+IFAD+NA+OSP+1PA-SIF-5159-P1-piyushhhhpundir_ -18/04/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3753-P1</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3753</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>daishwarya606</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9486</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="8" t="n">
+        <v>24.34</v>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDAFD+IFAD+NA+OSP+SIF-3753-P1-daishwarya606-18/04/206</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4568-P1</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4568</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>__.anuraaag</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9502</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="8" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>CTP-MSA+IFAD-MU+NA+OSP+SIF-4568-P1-__.anuraaag-09/03/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5983-P1</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5983</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>peachynush</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9528</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="8" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDRST+MU+NA+IHP+1PA-SIF-5983-P1-peachynush-10/05/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3010-P2</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3010</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>utkarsh_shhh</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9471</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="8" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>CLP-MSA+IFAD+NA+OSP+SIF-3010-P2-utkarsh_shhh-11/04/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7342-P1</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7342</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>_palaksomani</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9546</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="8" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>CTP-SDFAK+IFAD-MU+NA+OSP+1PA-SIF-7342-P1-_palaksomani-5/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3982-P1</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3982</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>khushimodiii</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>— (handle changed / not live)</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="8" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>CTP-BST+IFAD-MU+NA+OSP+SIF-3982-P1-khushimodiii-16/05/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5121-P1</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5121</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>stylewithumar</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9513</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="8" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SMDPT+IFAD+NA+IHP+1PA-SIF-5121-P1-stylewithumar-13/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1826-P1</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1826</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>the.blissful.stories</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9442</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="8" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>CTP-BST+IFAD-MU+NA+OSP+SIF-1826-P1-the.blissful.stories-03/05/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2340-P1</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2340</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>thesharannair</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9029</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F115" s="8" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SMFLK+IFAD+NA+IHP+1PA-SIF-2340-P1-ved.sawlani_16/12/25 | CLP-SMFLK+IFAD+NA+OSP+SIF-2340-P1-ved.sawlani-18/04/26-A0 | CTP-MSA+IFAD+NA+OSP+SIF-2340-P1-ved.sawlani-13/05/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1494-P1</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1494</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>vinayak_archive</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9423</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="8" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>CTP-MSA+IFAD-MU+NA+OSP+SIF-1494-P1-vinayak_archive -13/05/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2066-P2</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2066</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>muskaanuppalofficial</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>SIF-8852</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" s="8" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDAMK+IFAD-MU+NA+IHP+SIF-2066-P2-muskaanuppalofficial-27/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4079-P1</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4079</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>ekkum_kaur</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>— (handle changed / not live)</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" s="8" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>CTP-TW+IFAD+NA+OSP+SIF-4079-P1-ekkum_kaur-14/03/26-ADD-OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3951-P1</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3951</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>mr.priyank__01</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9483</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="8" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>CLP-MSA+IFAD-MU+NA+OSP+SIF-3951-P1-mr.priyank__01-11/04/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7492-P1</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7492</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>meetttmm</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9547</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="8" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SMDPT+IFAD+NA+IHP+1PA-SIF-7492-P1-meetttmm -Fabric Education-13/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4668-P1</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4668</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>dishakaaa</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9504</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDRST+IFAD-MU+NA+OSP+SIF-4668-P1-dishakaaa-14/03/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2620-P1</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2620</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>manohar_kondeti</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9461</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>CLP-MSA+IFAD+NA+OSP+SIF-2620-P1-manohar_kondeti-20/04/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5883-P1</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5883</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>paras_soul</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9526</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F123" s="8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SMELMS+IFAD+NA+OSP+SIF-5883-P1-paras_soul-11/04/26 | CLP-SMELMS+IFAD+NA+OSP+SIF-5883-P1-paras_soul-11/04/26 – Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1219-P1</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1219</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>mehakpurswani_</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9420</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1219-P1-mehakpurswani_-IFAD_13/11/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>SIF-84-P1</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>SIF-84</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>payalagarwall_</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9556</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F125" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="3" t="inlineStr">
+        <is>
+          <t>BR_IFAD_SIF-84-P1-payalagarwall__28/02/25_HP_12/01/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>SIF-916-P1</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>SIF-916</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>pinterest__muffin</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9494</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F126" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDALS+MU+NA+IHP+SIF-916-P1-pinterest__muffin_28/01/26 – Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4324-P1</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4324</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>@rupanjanauwu</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9499</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F127" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDELKB+FBP+NA+OSP+SIF-4324-P1-rupanjanauwu-28/02/26 – Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>SIF-186-P2</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>SIF-186</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>devna_sahrawat</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9414</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDALS+IFAD+NA+OSP+SIF-186-P2-devna_sahrawat-2/04/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>SIF-151-P1</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>SIF-151</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>twinning_damsel</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9432</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>CTP-BST_IFAD–SIF-151-P1-twinning_damsel_16/12/25_C0 – Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>SIF-293-P2</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>SIF-293</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>divyacyriac</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9466</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F130" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>CLP-BST+IFAD+NA+IHP+BR_IFAD_SIF-293-P2-divyacyriac_16/04/25_W+_12/01/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>SIF-18-P2</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>SIF-18</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>shailybakliwal059</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9407</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F131" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" s="3" t="inlineStr">
+        <is>
+          <t>SIF-18-P2-shailybakliwal059_13/11/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>SIF-839-P2</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>SIF-839</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>shefalithapa2</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>SIF-9421</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F132" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>SIF-839-P2-shefalithapa2_IFAD _13/11/25</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G132"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Post ID (in ad name)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Creator (if known)</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Their SIF</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Ads</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Spend (INR)</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Ad Names</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>PA-2272-P1</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Post ID exists nowhere — typo in ad name</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="8" t="n">
+        <v>133953.34</v>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>IFAD_SIF-1PA-2272-P1-shrishtibhardwaj_HP_26/12/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2078-P2</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Creator exists — wrong P-number in ad name</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>anjali_tatrari</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2078</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>7397.7</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>CTP-SMCFS+IFAD+NA+IHP+SIF-2078-P2-sumitchaharr-27/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1833-P4</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Creator exists — wrong P-number in ad name</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>rejo_oommen</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1833</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>3551.54</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>CTP-SMLFS+IFAD-MU+NA+IHP+SIF-1833-P4-iam_kushagra_0-21/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1842-P3</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Creator exists — wrong P-number in ad name</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>lata_mathpal</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1842</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>1907.06</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDASK+IFAD+NA+IHP+1PA-SIF-1842-P3-vaishfr-24/06/26-ERR | CLP-SDASK+IFAD+NA+IHP+SIF-1842-P3-vaishfr-24/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>SSIF-5452-P1</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Post ID exists nowhere — typo in ad name</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>1432.46</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDCSS+IFAD-MU+NA+OSP+1PA-SSIF-5452-P1-divyaunnyfilms-23/05/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>PASIF-6055-P1</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Post ID exists nowhere — typo in ad name</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>881.95</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>CTP-SDCCT+IFAD-MU+NA+IHP+1PASIF-6055-P1-pratibhaadubbeyy-20/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>SIF-661-P3</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Creator exists — wrong P-number in ad name</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>bee_vani_</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>SIF-661</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>609.3</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDALS+IFAD+NA+OSP+SIF-661-P3-stuti.rastogi_16/04/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2372-P4</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Creator exists — wrong P-number in ad name</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>_gouri._.krishna_</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2372</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>604.7</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>CTP-BST+IFAD+NA+OSP+SIF-2372-P4-_gouri._.krishna_-27/06/26 | CTP-BST+IFAD+NA+OSP+SIF-2372-P4-_gouri._.krishna_-27/06/26 - Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>SIF-0791-P1</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Post ID exists nowhere — typo in ad name</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n"/>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>544.5700000000001</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDFLK_IFAD–SIF-0791-P1-vijannie_16/12/25 | CLP-SDFLK_IFAD–SIF-0791-P1-vijannie_16/12/25 – Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7472-P3</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Creator exists — wrong P-number in ad name</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>engineeronvacay</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7472</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>462.35</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>CTP-BST+IFAD+NA+OSP+SIF-7472-P3-jyoti_negi_-27/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4013-P1</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Post ID exists nowhere — typo in ad name</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>409.06</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDFSK+IFAD-MU+NA+OSP+SIF-4013-P1-SIF-4013-P1-anushkaaa.a3_19/01/26 | CLP-SDFSK+IFAD-MU+NA+OSP+SIF-4013-P1-SIF-4013-P1-anushkaaa.a3_19/01/26 – Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2437-P1</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Post ID exists nowhere — typo in ad name</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDFSK+IFAD+NA+OSP+SIF-2437-P1-shreya.batraaa-03/05/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7937-P31</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Creator exists — wrong P-number in ad name</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>shubhi.repo</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7937</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>300.93</v>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>CTP-SDCFD+IFAD+NA+IHP+SIF-7937-P31- nymishasuggu-24/06/26 | CTP-SDCFD+IFAD+NA+IHP+SIF-7937-P31- nymishasuggu-27/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>SIFSIF-907-P2</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Post ID exists nowhere — typo in ad name</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>236.33</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>CLP-CTP+IFAD+NA+OSP+SIFSIF-907-P2-@allaboutprernaa-9/05/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>SIF-3327-P1</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Post ID exists nowhere — typo in ad name</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>187.67</v>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>CTP-BST+IFAD-MU+NA+OSP+1PA-SIF-3327-P1-nitya_sehgal -16/04/26 | CTP-BST+IFAD-MU+NA+OSP+SIF-3327-P1-nitya_sehgal -16/04/26 – Copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7471-P14</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Creator exists — wrong P-number in ad name</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>a.wishxx</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7471</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>158.57</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SMFRT+IFAD+NA+IHP+1PA-SIF-7471-P14-nikk__d -27/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7472-P11</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Creator exists — wrong P-number in ad name</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>engineeronvacay</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>SIF-7472</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>131.92</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>CTP-BST+IFAD-MU+NA+OSP+SIF-7472-P11-iamsnehakhan-27/05/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>SIF-6925-P2</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Creator exists — wrong P-number in ad name</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>pradeep._rajpurohit._</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>SIF-6925</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>87.81</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>CTP-MSA+IFAD-MU+NA+OSP+SIF-6925-P2-pradeep._rajpurohit._ -10/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1682-P3</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Creator exists — wrong P-number in ad name</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>disha_gupta26</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1682</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>81.23999999999999</v>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDAMK+IFAD-MU+NA+IHP+SIF-1682-P3-ritikanawani_-27/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>SIF-2943-P1</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Post ID exists nowhere — typo in ad name</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>70.33</v>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>CTP-MTW+IFAD+NA+OSP+SIF-2943-P1-piyushhhpundir__09/01/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5787-P2</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Creator exists — wrong P-number in ad name</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>kala_wati_</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5787</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>CTP-BST+IFAD+NA+OSP+SIF-5787-P2-kala_wati_-27/03/26-ADD-OFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1743-P2</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Creator exists — wrong P-number in ad name</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>yxshmeet</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>SIF-1743</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDJRT+IFAD+NA+IHP+SIF-1743-P2- yashikkajain-27/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>SSIF-1931-P1</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Post ID exists nowhere — typo in ad name</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDFSK+IFAD-MU+NA+OSP+SSIF-1931-P1-ankkriita-03/05/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>SIF-4020-P1</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Post ID exists nowhere — typo in ad name</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n"/>
+      <c r="E25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SMFLK+IFAD-MU+NA+OSP+SIF-4020-P1-_the_adhyapak_-19/02/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>SIF-5748-P1</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Post ID exists nowhere — typo in ad name</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n"/>
+      <c r="E26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDALS+IFAD-MU+NA+OSP+SIF-5748-P1-snehahaha1-31/03/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>KSIF-3768-P1</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Post ID exists nowhere — typo in ad name</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>CLP-SDALS+IFAD+NA+OSP+kSIF-3768-P1-rishika_71_22/01/26 – Copy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G27"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H1305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
